--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -1374,7 +1374,7 @@
         <v>136159865</v>
       </c>
       <c r="B8" t="n">
-        <v>96773</v>
+        <v>96776</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>136423160</v>
       </c>
       <c r="B11" t="n">
-        <v>92902</v>
+        <v>92905</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>136423202</v>
       </c>
       <c r="B20" t="n">
-        <v>92935</v>
+        <v>92938</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>136423088</v>
       </c>
       <c r="B48" t="n">
-        <v>106483</v>
+        <v>106486</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -1374,7 +1374,7 @@
         <v>136159865</v>
       </c>
       <c r="B8" t="n">
-        <v>96776</v>
+        <v>96777</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>136423160</v>
       </c>
       <c r="B11" t="n">
-        <v>92905</v>
+        <v>92906</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>136423202</v>
       </c>
       <c r="B20" t="n">
-        <v>92938</v>
+        <v>92939</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>136423088</v>
       </c>
       <c r="B48" t="n">
-        <v>106486</v>
+        <v>106487</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -1374,7 +1374,7 @@
         <v>136159865</v>
       </c>
       <c r="B8" t="n">
-        <v>96777</v>
+        <v>96782</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>136423160</v>
       </c>
       <c r="B11" t="n">
-        <v>92906</v>
+        <v>92911</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>136423202</v>
       </c>
       <c r="B20" t="n">
-        <v>92939</v>
+        <v>92944</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>136423088</v>
       </c>
       <c r="B48" t="n">
-        <v>106487</v>
+        <v>106492</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 3152-2025 artfynd.xlsx
+++ b/artfynd/A 3152-2025 artfynd.xlsx
@@ -1706,7 +1706,7 @@
         <v>136423160</v>
       </c>
       <c r="B11" t="n">
-        <v>92911</v>
+        <v>92913</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>136423202</v>
       </c>
       <c r="B20" t="n">
-        <v>92944</v>
+        <v>92946</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>136423088</v>
       </c>
       <c r="B48" t="n">
-        <v>106492</v>
+        <v>106494</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
